--- a/data/output/evaluasi_61.xlsx
+++ b/data/output/evaluasi_61.xlsx
@@ -8,6 +8,20 @@
   </bookViews>
   <sheets>
     <sheet name="6100" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="6111" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="6102" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="6110" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="6101" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6103" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6172" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="6104" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="6106" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="6171" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="6107" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="6108" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="6109" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="6105" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="6112" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,7 +489,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-91.3625767802598</v>
+        <v>-90.26855096538135</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -484,7 +498,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -503,7 +517,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-78.34477383213498</v>
+        <v>-75.03313461843129</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -512,7 +526,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -527,20 +541,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39.42373007125704</v>
+        <v>-83.04057532242696</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25</t>
+          <t>adhb_pi_q3-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -555,20 +569,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>54.68779117484826</v>
+        <v>38.28405462772895</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q2-25</t>
+          <t>adhb_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -583,20 +597,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-91.65878771224796</v>
+        <v>30.3447467960813</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25</t>
+          <t>adhb_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -611,20 +625,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-86.53329464019046</v>
+        <v>45.76995667509839</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>adhk_pi_q2-25</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -643,16 +657,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>77.80488709317109</v>
+        <v>-91.17733114317963</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25</t>
+          <t>adhk_pi_q1-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -671,16 +685,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>73.73230672522702</v>
+        <v>-87.80979348932912</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q2-25</t>
+          <t>adhk_pi_q2-25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -695,20 +709,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.005086957051657</v>
+        <v>-89.67881688282793</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25 vs distribusi_pi_q1-25.1</t>
+          <t>adhk_pi_q3-25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -723,20 +737,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7669598797156787</v>
+        <v>76.06034949314956</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>distribusi_pi_q2-25 vs distribusi_pi_q2-25.1</t>
+          <t>adhk_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -751,20 +765,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7.135675066250583</v>
+        <v>64.6215361852984</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>distribusi_net_ekspor_q1-25 vs distribusi_net_ekspor_q1-25.1</t>
+          <t>adhk_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -779,20 +793,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.068790109361601</v>
+        <v>163.9490180169595</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>distribusi_net_ekspor_q2-25 vs distribusi_net_ekspor_q2-25.1</t>
+          <t>adhk_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -807,20 +821,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.529297582612153</v>
+        <v>4.091046690047883</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
+          <t>q-to-q_pklnprt_q1-25 vs q-to-q_pklnprt_q1-25.1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -835,20 +849,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1.087510305882333</v>
+        <v>1.711911654345623</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25 vs y-on-y_pklnprt_q1-25.1</t>
+          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -863,20 +877,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.6915791644893757</v>
+        <v>5.675404342380461</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -891,20 +905,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.087510305882333</v>
+        <v>1.256770488824759</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25 vs c-to-c_pklnprt_q1-25.1</t>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -923,16 +937,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.6915791644893757</v>
+        <v>-8.53130845652527</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+          <t>q-to-q_pmtb_q1-25 vs q-to-q_pmtb_q1-25.1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -947,20 +961,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.0204103920541</v>
+        <v>5.348424312649807</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
         </is>
       </c>
     </row>
@@ -975,20 +989,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.006841902963309</v>
+        <v>7.73633385956501</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+          <t>y-on-y_pklnprt_q2-25 vs y-on-y_pklnprt_q2-25.1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1003,20 +1017,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.084892749412937</v>
+        <v>6.729620960418991</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q2-25 vs implisit_q-to-q_pmtb_q2-25.1</t>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
         </is>
       </c>
     </row>
@@ -1035,16 +1049,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.602018779106803</v>
+        <v>0.6030250915138382</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25 vs implisit_y-on-y_pklnprt_q1-25.1</t>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
         </is>
       </c>
     </row>
@@ -1059,20 +1073,3156 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2.580051048314216</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>61</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kalimantan Barat</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>2.473742868734714</v>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="D24" t="n">
+        <v>7.255240431192143</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q2-25 vs y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>61</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kalimantan Barat</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>9.760791106469116</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>61</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kalimantan Barat</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3.274508694490724</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q2-25 vs c-to-c_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>61</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kalimantan Barat</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4.403906493693175</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25 vs c-to-c_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>61</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kalimantan Barat</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.6030250915138382</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>61</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kalimantan Barat</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2.688248856435512</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q2-25 vs c-to-c_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>61</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kalimantan Barat</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>5.165842374283685</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25 vs c-to-c_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>61</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kalimantan Barat</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.7697202888258238</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>61</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kalimantan Barat</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-1.012723831514366</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>61</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kalimantan Barat</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.7724654204103205</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q2-25 vs implisit_q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>61</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kalimantan Barat</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1.321162981526743</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q1-25 vs implisit_q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>61</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kalimantan Barat</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1.18751686130538</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q2-25 vs implisit_q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>61</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Kalimantan Barat</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1.838973420196348</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25 vs implisit_q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>61</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Kalimantan Barat</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2.307645767973339</v>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>implisit_y-on-y_pklnprt_q2-25 vs implisit_y-on-y_pklnprt_q2-25.1</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>61</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Kalimantan Barat</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>4.085893874953045</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25 vs implisit_y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.072645746223814</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.02278789284386917</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.716947413052074</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.117314695788557</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.181264300917477</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.431767520935701</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7.376238457119603</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6171</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.6188713910743856</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6107</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Sintang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.05499774796018866</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6107</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sintang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.107191646691081</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6107</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sintang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7.133979485262556</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6107</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sintang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.138592268436016</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6108</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas Hulu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.71233013488633</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6108</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas Hulu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.133068727275685</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6109</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Sekadau</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.091899252619538</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6109</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sekadau</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.295866983654919</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6109</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sekadau</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>15.31387869178458</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6105</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Sanggau</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5.78260514517758</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6105</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sanggau</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.8475122273431638</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6105</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sanggau</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.6218307110869884</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6112</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2501293462931503</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6112</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6.31814069773496</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6112</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.5490194558735588</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6112</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.685308519640051</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>91.75724850997274</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>distribusi_pmtb_q2-25_ril vs distribusi_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-5 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-65.02022179109576</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>distribusi_net_ekspor_q2-25_ril vs distribusi_net_ekspor_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-5 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>214.2584458947384</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q2-25_ril vs q-to-q_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>225.8463424396908</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q2-25_ril vs y-on-y_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>114.8648020738344</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q2-25_ril vs c-to-c_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.8355412671141099</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-4.245196222604481</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>19.46673833818252</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>264.6754273701057</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6111</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kayong Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>167.013749900196</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6102</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkayang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.269960396471367</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6102</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkayang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-4.934655436894734</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6102</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkayang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4.680755718955986</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6102</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkayang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.925138768163257</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6102</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkayang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.253759971481319</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Melawi</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.10859870777081</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Melawi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.594006541632745</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Melawi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.20565953775001</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Melawi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.955859612528009</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6101</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Sambas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-4.207826234332359</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6101</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sambas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.927413187413022</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6101</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sambas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4.313728492325408</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6103</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Landak</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.479649716168023</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-5.343134434676545</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.505833864895359</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.137699098086361</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9302433374399932</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.347217942607244</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.267202679995562</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6172</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-3.896182163503378</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3.84838384528838</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6.601686348621058</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>28.12630592099484</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9.865037593186985</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2277881663598549</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-28.92353142961843</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.269522789367427</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-42.45089765698789</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.231208190357163</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6104</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Mempawah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5.489881098437413</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.447611733566462</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.03958741554033953</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>24.60052569050997</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.994351943400388</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>23.06221519001501</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.331145369963104</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.5246523222811861</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.27733646244089</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.969571200229961</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6106</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Ketapang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.918507124277413</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_61.xlsx
+++ b/data/output/evaluasi_61.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
